--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_29-08-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_29-08-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.155); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c8db3d85+79397]
-	GetHandleVerifier [0x0x7ff7c8db3de0+79488]
-	(No symbol) [0x0x7ff7c8b5c0fa]
-	(No symbol) [0x0x7ff7c8bb2fd6]
-	(No symbol) [0x0x7ff7c8bb328c]
-	(No symbol) [0x0x7ff7c8c06537]
-	(No symbol) [0x0x7ff7c8bdb1df]
-	(No symbol) [0x0x7ff7c8c03344]
-	(No symbol) [0x0x7ff7c8bdaf73]
-	(No symbol) [0x0x7ff7c8ba41b1]
-	(No symbol) [0x0x7ff7c8ba4f43]
-	GetHandleVerifier [0x0x7ff7c907e1ed+3005069]
-	GetHandleVerifier [0x0x7ff7c907831d+2980797]
-	GetHandleVerifier [0x0x7ff7c9097e0d+3110573]
-	GetHandleVerifier [0x0x7ff7c8dcd6de+184190]
-	GetHandleVerifier [0x0x7ff7c8dd516f+215567]
-	GetHandleVerifier [0x0x7ff7c8dbc974+115220]
-	GetHandleVerifier [0x0x7ff7c8dbcb29+115657]
-	GetHandleVerifier [0x0x7ff7c8da3268+11016]
+	GetHandleVerifier [0x0x7ff606bf3d85+79397]
+	GetHandleVerifier [0x0x7ff606bf3de0+79488]
+	(No symbol) [0x0x7ff60699c0fa]
+	(No symbol) [0x0x7ff6069f2fd6]
+	(No symbol) [0x0x7ff6069f328c]
+	(No symbol) [0x0x7ff606a46537]
+	(No symbol) [0x0x7ff606a1b1df]
+	(No symbol) [0x0x7ff606a43344]
+	(No symbol) [0x0x7ff606a1af73]
+	(No symbol) [0x0x7ff6069e41b1]
+	(No symbol) [0x0x7ff6069e4f43]
+	GetHandleVerifier [0x0x7ff606ebe1ed+3005069]
+	GetHandleVerifier [0x0x7ff606eb831d+2980797]
+	GetHandleVerifier [0x0x7ff606ed7e0d+3110573]
+	GetHandleVerifier [0x0x7ff606c0d6de+184190]
+	GetHandleVerifier [0x0x7ff606c1516f+215567]
+	GetHandleVerifier [0x0x7ff606bfc974+115220]
+	GetHandleVerifier [0x0x7ff606bfcb29+115657]
+	GetHandleVerifier [0x0x7ff606be3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
